--- a/MotPsy_V57_APA_dates_corrigees.xlsx
+++ b/MotPsy_V57_APA_dates_corrigees.xlsx
@@ -227,7 +227,7 @@
 — Klein, M. (2013). La psychanalyse des enfants. PUF, p. 68. (Éd. originale 1932.)</t>
   </si>
   <si>
-    <t xml:space="preserve">MP6_Klein_Fans.jpg | Réunion de Fans de Mélanie Klein ?</t>
+    <t xml:space="preserve">MP6_Klein_Fans.jpg | Fans de Mélanie Klein attendant sa venue au Monde...</t>
   </si>
   <si>
     <t>lundi</t>
